--- a/testakten/unfallversicherung-arbeitsunfall-lagerleiter-sturz-trier/30_verletztengeld_mde_rentenberechnung.xlsx
+++ b/testakten/unfallversicherung-arbeitsunfall-lagerleiter-sturz-trier/30_verletztengeld_mde_rentenberechnung.xlsx
@@ -449,6 +449,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -462,7 +463,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Regelentgelt kalendertaeglich</t>
+          <t>Regelentgelt kalendertäglich</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -472,7 +473,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verletztengeld kalendertaeglich</t>
+          <t>Verletztengeld kalendertäglich</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -621,10 +622,11 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hinweis: Verletztengeld betraegt 80 Prozent des Regelentgelts, gedeckelt auf das Nettoarbeitsentgelt (Paragraf 47 SGB VII). Die Berechnung ist vorlaeufig und wurde mangels Anerkennung als Arbeitsunfall bislang nicht ausgezahlt.</t>
+          <t>Hinweis: Verletztengeld beträgt 80 Prozent des Regelentgelts, gedeckelt auf das Nettoarbeitsentgelt (Paragraf 47 SGB VII). Die Berechnung ist vorläufig und wurde mangels Anerkennung als Arbeitsunfall bislang nicht ausgezahlt.</t>
         </is>
       </c>
     </row>
@@ -651,10 +653,11 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Einschaetzung der Minderung der Erwerbsfaehigkeit (MdE)</t>
-        </is>
-      </c>
-    </row>
+          <t>Einschätzung der Minderung der Erwerbsfähigkeit (MdE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -690,7 +693,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verlust der Armhebefaehigkeit ueber Schulterhoehe bei sonst freier Beweglichkeit 20 bis 30 vom Hundert</t>
+          <t>Verlust der Armhebefähigkeit über Schulterhöhe bei sonst freier Beweglichkeit 20 bis 30 vom Hundert</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -702,17 +705,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aussenrotation</t>
+          <t>Außenrotation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>endgradig schmerzhaft eingeschraenkt</t>
+          <t>endgradig schmerzhaft eingeschränkt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>geringe zusaetzliche Funktionsminderung</t>
+          <t>geringe zusätzliche Funktionsminderung</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -734,7 +737,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>keine eigenstaendige Erhoehung</t>
+          <t>keine eigenständige Erhöhung</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -743,24 +746,24 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gutachterliche Gesamt-MdE (vorlaeufig)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+          <t>Gutachterliche Gesamt-MdE (vorläufig)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>20 vom Hundert</t>
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hinweis: Eine MdE von mindestens 20 vom Hundert ueber die 26. Woche nach dem Arbeitsunfall hinaus begruendet dem Grunde nach einen Anspruch auf Verletztenrente nach Paragraf 56 SGB VII. Eine Nachuntersuchung nach zwoelf Monaten wurde vom Sachverstaendigen empfohlen.</t>
+          <t>Hinweis: Eine MdE von mindestens 20 vom Hundert über die 26. Woche nach dem Arbeitsunfall hinaus begründet dem Grunde nach einen Anspruch auf Verletztenrente nach Paragraf 56 SGB VII. Eine Nachuntersuchung nach zwölf Monaten wurde vom Sachverständigen empfohlen.</t>
         </is>
       </c>
     </row>
@@ -786,14 +789,15 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vorlaeufige Berechnung der Verletztenrente</t>
-        </is>
-      </c>
-    </row>
+          <t>Vorläufige Berechnung der Verletztenrente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Berechnungsgroesse</t>
+          <t>Berechnungsgröße</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Erlaeuterung</t>
+          <t>Erläuterung</t>
         </is>
       </c>
     </row>
@@ -820,7 +824,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bruttojahresverdienst der zwoelf Monate vor dem Unfall, 12 mal 4180 Euro</t>
+          <t>Bruttojahresverdienst der zwölf Monate vor dem Unfall, 12 mal 4180 Euro</t>
         </is>
       </c>
     </row>
@@ -837,7 +841,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vorlaeufige gutachterliche Einschaetzung</t>
+          <t>Vorläufige gutachterliche Einschätzung</t>
         </is>
       </c>
     </row>
@@ -888,14 +892,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Teilrente geteilt durch zwoelf Monate</t>
-        </is>
-      </c>
-    </row>
+          <t>Teilrente geteilt durch zwölf Monate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hinweis: Die Berechnung ist eine rentenberaterliche Modellrechnung auf Grundlage der vorlaeufigen MdE-Einschaetzung von 20 vom Hundert und dient der Vorbereitung des Klageverfahrens. Endgueltig entscheidet die Berufsgenossenschaft beziehungsweise das Sozialgericht nach Vorliegen der Nachuntersuchung.</t>
+          <t>Hinweis: Die Berechnung ist eine rentenberaterliche Modellrechnung auf Grundlage der vorläufigen MdE-Einschätzung von 20 vom Hundert und dient der Vorbereitung des Klageverfahrens. Endgültig entscheidet die Berufsgenossenschaft beziehungsweise das Sozialgericht nach Vorliegen der Nachuntersuchung.</t>
         </is>
       </c>
     </row>
